--- a/planilla/Planilla_inicial_auditoria.xlsx
+++ b/planilla/Planilla_inicial_auditoria.xlsx
@@ -25,7 +25,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MEDIDAS" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONCEPTOS" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INDICES" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CARGAS" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXPENSA_NUEVA" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXPENSA_ESTADO" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CARGAS" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16469,7 +16471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q58"/>
+  <dimension ref="A1:Q57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -20026,7 +20028,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>S2-N-02</t>
+          <t>S2-N-03</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -20036,24 +20038,26 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>N-02</t>
+          <t>N-03</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>El total de deudas con proveedores es menor que lo pendiente solo del mes</t>
+          <t>Cobros que no se sabe de qué lote son</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr"/>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>IMPORTANTE</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr"/>
+          <t>A REVISAR</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>902350</v>
+      </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>sin monto</t>
+          <t>saldo en riesgo</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -20063,7 +20067,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>Pasa en 07, 08 y 10/2026.</t>
+          <t>Hay cobros sin identificar todos los meses.</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
@@ -20073,7 +20077,7 @@
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>Listado de deudas con cada proveedor.</t>
+          <t>Identificar cada cobro y su lote.</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -20097,7 +20101,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>S2-N-03</t>
+          <t>S2-N-04</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -20107,36 +20111,36 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>N-03</t>
+          <t>N-04</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Cobros que no se sabe de qué lote son</t>
+          <t>Fondo ordinario en negativo: gastos pagados con el fondo extraordinario</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>IMPORTANTE</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>902350</v>
+        <v>350258.39</v>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>saldo en riesgo</t>
+          <t>una vez</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>Hay cobros sin identificar todos los meses.</t>
+          <t>Pasó en 08/2026.</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
@@ -20146,7 +20150,7 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>Identificar cada cobro y su lote.</t>
+          <t>Regla escrita de uso de cada fondo.</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -20170,7 +20174,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>S2-N-04</t>
+          <t>S2-N-05</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -20180,36 +20184,34 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>N-04</t>
+          <t>N-05</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Fondo ordinario en negativo: gastos pagados con el fondo extraordinario</t>
+          <t>Cuentas sin fondo de reserva</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr"/>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>IMPORTANTE</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>350258.39</v>
-      </c>
+          <t>A REVISAR</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>una vez</t>
+          <t>sin monto</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>Pasó en 08/2026.</t>
+          <t>No figura en ningún mes.</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
@@ -20219,7 +20221,7 @@
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>Regla escrita de uso de cada fondo.</t>
+          <t>Definir un fondo de reserva en asamblea.</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -20243,7 +20245,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>S2-N-05</t>
+          <t>S2-N-06</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -20253,12 +20255,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>N-05</t>
+          <t>N-06</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Cuentas sin fondo de reserva</t>
+          <t>Dos cuentas bancarias: doble mantenimiento y doble impuesto</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr"/>
@@ -20267,10 +20269,12 @@
           <t>A REVISAR</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr"/>
+      <c r="G50" t="n">
+        <v>90750</v>
+      </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>sin monto</t>
+          <t>por mes</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -20280,17 +20284,17 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>No figura en ningún mes.</t>
+          <t>Se paga todos los meses.</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>Flujo de fondos</t>
+          <t>Bancarios</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>Definir un fondo de reserva en asamblea.</t>
+          <t>Una sola cuenta, a nombre del barrio.</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -20314,7 +20318,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>S2-N-06</t>
+          <t>S2-N-07</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -20324,12 +20328,12 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>N-06</t>
+          <t>N-07</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Dos cuentas bancarias: doble mantenimiento y doble impuesto</t>
+          <t>Recargo por pagar la luz fuera de término</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr"/>
@@ -20339,7 +20343,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>90750</v>
+        <v>2165.08</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
@@ -20353,17 +20357,17 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>Se paga todos los meses.</t>
+          <t>08 y 10/2026 al 2.º vencimiento.</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>Bancarios</t>
+          <t>Servicios públicos</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>Una sola cuenta, a nombre del barrio.</t>
+          <t>Débito automático o pago a término.</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -20387,7 +20391,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>S2-N-07</t>
+          <t>S2-N-08</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -20397,12 +20401,12 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>N-07</t>
+          <t>N-08</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Recargo por pagar la luz fuera de término</t>
+          <t>Lote de coeficiente reducido (65%) sin reglamento informado</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr"/>
@@ -20411,12 +20415,10 @@
           <t>A REVISAR</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>2165.08</v>
-      </c>
+      <c r="G52" s="3" t="inlineStr"/>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>por mes</t>
+          <t>sin monto</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -20426,17 +20428,17 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>08 y 10/2026 al 2.º vencimiento.</t>
+          <t>Se aplica todos los meses.</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>Servicios públicos</t>
+          <t>Resumen</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>Débito automático o pago a término.</t>
+          <t>Reglamento o acta de coeficientes.</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -20460,7 +20462,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>S2-N-08</t>
+          <t>S2-N-09</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -20470,18 +20472,18 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>N-08</t>
+          <t>N-09</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Lote de coeficiente reducido (65%) sin reglamento informado</t>
+          <t>Cargos particulares +237% en 10/2026 sin detalle</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr"/>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>IMPORTANTE</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr"/>
@@ -20492,12 +20494,12 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>Se aplica todos los meses.</t>
+          <t>Varían mes a mes sin explicación.</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
@@ -20507,7 +20509,7 @@
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>Reglamento o acta de coeficientes.</t>
+          <t>Detalle por concepto y fondo.</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -20531,7 +20533,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>S2-N-09</t>
+          <t>S2-N-10</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -20541,12 +20543,12 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>N-09</t>
+          <t>N-10</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Cargos particulares +237% en 10/2026 sin detalle</t>
+          <t>Seguridad: a La Huella se le liquida el mismo importe al centavo que a Senderos II</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr"/>
@@ -20563,22 +20565,22 @@
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>Varían mes a mes sin explicación.</t>
+          <t>Pasó en 08, 09 y 10/2026.</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>Resumen</t>
+          <t>Consolidado barrios</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>Detalle por concepto y fondo.</t>
+          <t>Facturas de seguridad de cada barrio.</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -20602,7 +20604,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>S2-N-10</t>
+          <t>S2-N-11</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -20612,24 +20614,26 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>N-10</t>
+          <t>N-11</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Seguridad: a La Huella se le liquida el mismo importe al centavo que a Senderos II</t>
+          <t>AdminProp sube todos los meses (+42% en 4 meses)</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>IMPORTANTE</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr"/>
+          <t>A REVISAR</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>32964</v>
+      </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>sin monto</t>
+          <t>por mes</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -20639,17 +20643,17 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>Pasó en 08, 09 y 10/2026.</t>
+          <t>Aumenta en cada liquidación.</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>Consolidado barrios</t>
+          <t>Abonos de servicios</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>Facturas de seguridad de cada barrio.</t>
+          <t>Definir si lo paga el barrio o el administrador.</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -20673,7 +20677,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>S2-N-11</t>
+          <t>S2-N-12</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -20683,12 +20687,12 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>N-11</t>
+          <t>N-12</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>AdminProp sube todos los meses (+42% en 4 meses)</t>
+          <t>El total de expensas no es la suma de sus partes (centavos)</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr"/>
@@ -20698,31 +20702,31 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>32964</v>
+        <v>0.36</v>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>por mes</t>
+          <t>una vez</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>Aumenta en cada liquidación.</t>
+          <t>Pasó en 07 y 08/2026.</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>Abonos de servicios</t>
+          <t>Resumen</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>Definir si lo paga el barrio o el administrador.</t>
+          <t>Que el total salga de sumar sus partes.</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -20746,32 +20750,36 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>S2-N-12</t>
+          <t>LH-LH-10</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>LH</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>N-12</t>
+          <t>LH-10</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>El total de expensas no es la suma de sus partes (centavos)</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr"/>
+          <t>En 10/2026 se repartió más de lo que se gastó</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Se repartieron $ 956.782,24 más que el gasto (9,5%), $ 45.561 por lote.</t>
+        </is>
+      </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>CRÍTICO</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.36</v>
+        <v>956782.24</v>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
@@ -20780,12 +20788,12 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>Pasó en 07 y 08/2026.</t>
+          <t>Repite el esquema de 09/2026 (H01).</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
@@ -20795,12 +20803,12 @@
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>Que el total salga de sumar sus partes.</t>
+          <t>Composición de la base y devolución de la diferencia.</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>PENDIENTE DE RECLAMAR</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr"/>
@@ -20811,83 +20819,6 @@
       </c>
       <c r="P57" s="3" t="inlineStr"/>
       <c r="Q57" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>LH-LH-10</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>LH</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>LH-10</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>En 10/2026 se repartió más de lo que se gastó</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>Se repartieron $ 956.782,24 más que el gasto (9,5%), $ 45.561 por lote.</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>CRÍTICO</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>956782.24</v>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>una vez</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>Repite el esquema de 09/2026 (H01).</t>
-        </is>
-      </c>
-      <c r="K58" s="3" t="inlineStr">
-        <is>
-          <t>Resumen</t>
-        </is>
-      </c>
-      <c r="L58" s="3" t="inlineStr">
-        <is>
-          <t>Composición de la base y devolución de la diferencia.</t>
-        </is>
-      </c>
-      <c r="M58" s="3" t="inlineStr">
-        <is>
-          <t>PENDIENTE DE RECLAMAR</t>
-        </is>
-      </c>
-      <c r="N58" s="3" t="inlineStr"/>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="P58" s="3" t="inlineStr"/>
-      <c r="Q58" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -21806,7 +21737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22621,7 +22552,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>S2-FLUJO-5</t>
+          <t>S2-FLUJO-6</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -22635,18 +22566,18 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>El total de saldos pendientes de pago debería ser igual o mayor que lo pendiente solo del mes, porque lo incluye. En 07, 08 y 10/2026 es menor: los dos números no pueden ser correctos a la vez. Pedir el listado de deudas con cada proveedor.</t>
+          <t>En 09/2026 se repartió $ 1.627.054,66 más que lo gastado como "previsión de morosidad" (H01). En 10/2026 los lotes con deuda pagaron (de 5 a 4 lotes, $ 2,6 M menos de deuda) y la previsión no se devolvió ni se acreditó.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>S2-FLUJO-6</t>
+          <t>S2-FLUJO-7</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -22660,18 +22591,18 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>En 09/2026 se repartió $ 1.627.054,66 más que lo gastado como "previsión de morosidad" (H01). En 10/2026 los lotes con deuda pagaron (de 5 a 4 lotes, $ 2,6 M menos de deuda) y la previsión no se devolvió ni se acreditó.</t>
+          <t>En 08/2026 el fondo ordinario cerró en negativo (−$ 350.258,39): se pagaron gastos ordinarios con plata del fondo extraordinario. No hay fondo de reserva.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>S2-FLUJO-7</t>
+          <t>S2-FLUJO-8</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -22685,18 +22616,18 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>En 08/2026 el fondo ordinario cerró en negativo (−$ 350.258,39): se pagaron gastos ordinarios con plata del fondo extraordinario. No hay fondo de reserva.</t>
+          <t>Saldo impago de la factura de seguridad de 08/2026 ($ 3.654.176,39) que no se resta del patrimonio (H20). Tampoco figura la deuda con los proveedores de cámaras que reconoce la administración ($ 23.784.934,20 según la auditoría, H11).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>S2-FLUJO-8</t>
+          <t>S2-FLUJO-9</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -22710,18 +22641,18 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Saldo impago de la factura de seguridad de 08/2026 ($ 3.654.176,39) que no se resta del patrimonio (H20). Tampoco figura la deuda con los proveedores de cámaras que reconoce la administración ($ 23.784.934,20 según la auditoría, H11).</t>
+          <t>Al 30/09/2026 los bancos suman $ 8.596.500,30 y la liquidación informa $ 3.631.914,46. Al 28/08/2026 solo Roela tenía $ 4.060.839,34, contra $ 698.625,16 informados en total. La diferencia puede deberse a pagos registrados y todavía no debitados, pero eso se demuestra con una conciliación bancaria, que la liquidación no presenta. La cuenta Roela está a nombre del administrador (H18). Faltan los extractos de Galicia de 08/2026 y de los dos bancos de 10/2026.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>S2-FLUJO-9</t>
+          <t>S2-ACUMULADO-1</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -22731,22 +22662,22 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>FLUJO</t>
+          <t>ACUMULADO</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Al 30/09/2026 los bancos suman $ 8.596.500,30 y la liquidación informa $ 3.631.914,46. Al 28/08/2026 solo Roela tenía $ 4.060.839,34, contra $ 698.625,16 informados en total. La diferencia puede deberse a pagos registrados y todavía no debitados, pero eso se demuestra con una conciliación bancaria, que la liquidación no presenta. La cuenta Roela está a nombre del administrador (H18). Faltan los extractos de Galicia de 08/2026 y de los dos bancos de 10/2026.</t>
+          <t>De 06 a 08/2026 solo se corrige lo que se puede verificar: la seguridad por lotes (para 06 y 07 la factura total se toma como el doble de lo liquidado, REVISAR), el equipo CCTV cobrado con presupuesto y el recargo de luz. No se corrigen el mantenimiento del Fideicomiso, la caja chica ni Telered porque esas liquidaciones no informan la base ni los comprobantes. Por eso la diferencia de esos meses es un piso: la real es mayor.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>S2-ACUMULADO-1</t>
+          <t>S2-ACUMULADO-2</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -22760,18 +22691,18 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>De 06 a 08/2026 solo se corrige lo que se puede verificar: la seguridad por lotes (para 06 y 07 la factura total se toma como el doble de lo liquidado, REVISAR), el equipo CCTV cobrado con presupuesto y el recargo de luz. No se corrigen el mantenimiento del Fideicomiso, la caja chica ni Telered porque esas liquidaciones no informan la base ni los comprobantes. Por eso la diferencia de esos meses es un piso: la real es mayor.</t>
+          <t>Proyección simple: supone que cada mes se repiten los desvíos de octubre (Telered, luz del Fideicomiso, caja chica, mantenimiento, seguridad por encima de la factura) salvo la obra de cámaras. No incluye aumentos de precios. Se calcula con el coeficiente del lote común (1 ÷ 17,65).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>S2-ACUMULADO-2</t>
+          <t>S2-RESUMEN-1</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -22781,22 +22712,22 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>ACUMULADO</t>
+          <t>RESUMEN</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Proyección simple: supone que cada mes se repiten los desvíos de octubre (Telered, luz del Fideicomiso, caja chica, mantenimiento, seguridad por encima de la factura) salvo la obra de cámaras. No incluye aumentos de precios. Se calcula con el coeficiente del lote común (1 ÷ 17,65).</t>
+          <t>En 09/2026 se repartieron $ 1.627.054,66 más de lo gastado (17%), llamado "previsión de morosidad", sin línea propia ni regla de devolución (H01). Los demás meses se repartieron unos $ 35 a $ 46 menos que el gasto, por redondeo de la cuota, sin informarlo.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>S2-RESUMEN-1</t>
+          <t>S2-RESUMEN-2</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -22810,18 +22741,18 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>En 09/2026 se repartieron $ 1.627.054,66 más de lo gastado (17%), llamado "previsión de morosidad", sin línea propia ni regla de devolución (H01). Los demás meses se repartieron unos $ 35 a $ 46 menos que el gasto, por redondeo de la cuota, sin informarlo.</t>
+          <t>El lote de coeficiente reducido paga el 65% de un lote común. La cuota del lote común es exactamente el repartido ÷ 17,65 lotes equivalentes. El coeficiente no figura en la liquidación ni hay reglamento que lo respalde (REVISAR).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>S2-RESUMEN-2</t>
+          <t>S2-RESUMEN-3</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -22835,18 +22766,18 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>El lote de coeficiente reducido paga el 65% de un lote común. La cuota del lote común es exactamente el repartido ÷ 17,65 lotes equivalentes. El coeficiente no figura en la liquidación ni hay reglamento que lo respalde (REVISAR).</t>
+          <t>Los cargos particulares (canon de obra y otros) los pagan solo algunos lotes. En 10/2026 subieron 237% sin detalle. La administración no publica qué conceptos son ni a qué fondo van.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>S2-RESUMEN-3</t>
+          <t>S2-RESUMEN-4</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -22860,18 +22791,18 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Los cargos particulares (canon de obra y otros) los pagan solo algunos lotes. En 10/2026 subieron 237% sin detalle. La administración no publica qué conceptos son ni a qué fondo van.</t>
+          <t>Diferencia entre lo que se repartió a los lotes y el gasto correcto. En 09/2026 incluye la previsión de $ 1.627.054,66. Las correcciones de cada rubro están en su hoja (bloque "Liquidación correcta") y su origen, en las notas de cada hoja.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>S2-RESUMEN-4</t>
+          <t>S2-RESUMEN-6</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -22885,18 +22816,18 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Diferencia entre lo que se repartió a los lotes y el gasto correcto. En 09/2026 incluye la previsión de $ 1.627.054,66. Las correcciones de cada rubro están en su hoja (bloque "Liquidación correcta") y su origen, en las notas de cada hoja.</t>
+          <t>En 07/2026 el total de expensas informado es $ 0,14 menor que repartido + particulares, y en 08/2026 $ 0,22 mayor. Son centavos, pero muestran que el total no sale de sumar sus partes: la liquidación no informa de dónde vienen.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>S2-RESUMEN-6</t>
+          <t>S2-RESUMEN-5</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -22910,18 +22841,18 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>En 07/2026 el total de expensas informado es $ 0,14 menor que repartido + particulares, y en 08/2026 $ 0,22 mayor. Son centavos, pero muestran que el total no sale de sumar sus partes: la liquidación no informa de dónde vienen.</t>
+          <t>Fuentes: liquidaciones de expensas de Senderos II de 06 a 10/2026, comprobantes cargados en la auditoría y extractos bancarios disponibles (Roela 07 a 09, Galicia 07 y 09). Las observaciones son indicadores para revisar, no acusaciones.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>S2-RESUMEN-5</t>
+          <t>S2-NOV-2026-10-1</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -22931,32 +22862,32 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>RESUMEN</t>
+          <t>NOVEDAD:2026-10:Mantenimiento Fideicomiso - espacios propios 80%</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Fuentes: liquidaciones de expensas de Senderos II de 06 a 10/2026, comprobantes cargados en la auditoría y extractos bancarios disponibles (Roela 07 a 09, Galicia 07 y 09). Las observaciones son indicadores para revisar, no acusaciones.</t>
+          <t>No es una baja real: desde octubre la luz del Fideicomiso sale del mantenimiento y se cobra aparte como «Luz sectores comunes» ($ 498.204). Mantenimiento propios + comunes ($ 1.181.915,45) más esa luz suman $ 1.680.119,45, contra $ 1.443.644,68 de septiembre: en realidad sube $ 236.474,77 (+16,4%).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TODOS-RESPALDO-1</t>
+          <t>S2-NOV-2026-10-2</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>TODOS</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>RESPALDO</t>
+          <t>NOVEDAD:2026-10:Electricidad sectores comunes - Fideicomiso</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -22964,39 +22895,39 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>"Completo" no quiere decir que el gasto esté bien: una obra puede tener factura y no ser un gasto ordinario. Solo dice que hay un documento por ese importe.</t>
+          <t>Es la luz que hasta septiembre estaba dentro del mantenimiento del Fideicomiso, con una cuenta industrial incluida (H28). Se cobra aparte desde octubre, sin aviso previo. Sumada al mantenimiento, el barrio paga $ 236.474,77 más que en septiembre.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>TODOS-RESPALDO-2</t>
+          <t>S2-NOV-2026-10-3</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>TODOS</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>RESPALDO</t>
+          <t>NOVEDAD:2026-10:Telered</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>La mayor parte del gasto es "parcial" cuando se cobra como una parte de documentos de otros (seguridad compartida, mantenimiento del Fideicomiso), sin informar la base ni el criterio.</t>
+          <t>Gravísimo: el 10/09/2026 el administrador informó por escrito que el abono bajaba de unos $ 200.000 ($ 192.855 en septiembre) a $ 100.000. En octubre se liquidaron $ 567.600, 5,7 veces lo prometido y sin factura. Además, el 15/09 el banco debitó $ 1.135.200 (H26).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TODOS-RESPALDO-3</t>
+          <t>TODOS-RESPALDO-1</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -23010,18 +22941,18 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>El tipo de respaldo se calcula solo con los comprobantes cargados y se puede corregir a mano en cada gasto.</t>
+          <t>"Completo" no quiere decir que el gasto esté bien: una obra puede tener factura y no ser un gasto ordinario. Solo dice que hay un documento por ese importe.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>TODOS-AHORROS-1</t>
+          <t>TODOS-RESPALDO-2</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -23031,22 +22962,22 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>AHORROS</t>
+          <t>RESPALDO</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>A: importes verificados en la liquidación correcta. B: mejoras de gestión; las marcadas como supuesto o propuesta hay que confirmarlas antes de usarlas como reclamo. Por lote común = ahorro del barrio × coeficiente del lote común.</t>
+          <t>La mayor parte del gasto es "parcial" cuando se cobra como una parte de documentos de otros (seguridad compartida, mantenimiento del Fideicomiso), sin informar la base ni el criterio.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TODOS-AHORROS-2</t>
+          <t>TODOS-RESPALDO-3</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -23056,22 +22987,22 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>AHORROS</t>
+          <t>RESPALDO</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>La exención de Ingresos Brutos depende de la situación fiscal del consorcio: consultarlo con un contador antes de pedirla.</t>
+          <t>El tipo de respaldo se calcula solo con los comprobantes cargados y se puede corregir a mano en cada gasto.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>TODOS-MATRIZ-1</t>
+          <t>TODOS-AHORROS-1</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -23081,7 +23012,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>AHORROS</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -23089,14 +23020,14 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Probabilidad: que el problema se repita o siga afectando en los próximos meses. Impacto: alto si la auditoría lo califica como crítico o si el monto anual equivalente supera $ 1.500.000; medio si es importante o supera $ 150.000; bajo en los demás casos.</t>
+          <t>A: importes verificados en la liquidación correcta. B: mejoras de gestión; las marcadas como supuesto o propuesta hay que confirmarlas antes de usarlas como reclamo. Por lote común = ahorro del barrio × coeficiente del lote común.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TODOS-MATRIZ-2</t>
+          <t>TODOS-AHORROS-2</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -23106,7 +23037,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>MATRIZ</t>
+          <t>AHORROS</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -23114,14 +23045,14 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Puntaje = probabilidad (alta 3, media 2, baja 1) × impacto (alto 3, medio 2, bajo 1). Urgente: 9. Alta: 6. Media: 3 o 4. Baja: 1 o 2.</t>
+          <t>La exención de Ingresos Brutos depende de la situación fiscal del consorcio: consultarlo con un contador antes de pedirla.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>TODOS-MATRIZ-3</t>
+          <t>TODOS-MATRIZ-1</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -23135,18 +23066,18 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Monto en juego: "por mes" se multiplica por 12; "una vez" es lo que hay que recuperar o aclarar; "saldo en riesgo" es plata o deuda mal documentada (no es una pérdida). Los montos se superponen: no se suman.</t>
+          <t>Probabilidad: que el problema se repita o siga afectando en los próximos meses. Impacto: alto si la auditoría lo califica como crítico o si el monto anual equivalente supera $ 1.500.000; medio si es importante o supera $ 150.000; bajo en los demás casos.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TODOS-PEDIDO-1</t>
+          <t>TODOS-MATRIZ-2</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -23156,38 +23087,88 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>PEDIDO</t>
+          <t>MATRIZ</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>El importe en juego no es lo que hay que devolver: es el monto del punto. Algunos se superponen. No se suman.</t>
+          <t>Puntaje = probabilidad (alta 3, media 2, baja 1) × impacto (alto 3, medio 2, bajo 1). Urgente: 9. Alta: 6. Media: 3 o 4. Baja: 1 o 2.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
+          <t>TODOS-MATRIZ-3</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>TODOS</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>MATRIZ</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Monto en juego: "por mes" se multiplica por 12; "una vez" es lo que hay que recuperar o aclarar; "saldo en riesgo" es plata o deuda mal documentada (no es una pérdida). Los montos se superponen: no se suman.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>TODOS-PEDIDO-1</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>TODOS</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>PEDIDO</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>El importe en juego no es lo que hay que devolver: es el monto del punto. Algunos se superponen. No se suman.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
           <t>TODOS-PEDIDO-2</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>TODOS</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>PEDIDO</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D57" t="n">
         <v>2</v>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>Las observaciones son indicadores para revisar, no acusaciones. Cada pedido busca el documento que confirma o descarta el punto.</t>
         </is>
@@ -23922,13 +23903,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23952,6 +23934,11 @@
           <t>Orden</t>
         </is>
       </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Que_Es</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -23972,6 +23959,11 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Cuotas de un plan de pagos del impuesto inmobiliario.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -23992,6 +23984,11 @@
       <c r="D3" t="n">
         <v>2</v>
       </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>La parte del barrio en el impuesto inmobiliario del predio.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -24012,6 +24009,11 @@
       <c r="D4" t="n">
         <v>3</v>
       </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>La parte del barrio en la luz de la iluminación de las calles troncales y las bombas de agua del predio.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -24032,6 +24034,11 @@
       <c r="D5" t="n">
         <v>4</v>
       </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Luz de los espacios del barrio (cuenta de EDENOR del barrio).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -24052,6 +24059,11 @@
       <c r="D6" t="n">
         <v>5</v>
       </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Control de plagas y desratización del perímetro, los lotes en obra y la entrada.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -24072,6 +24084,11 @@
       <c r="D7" t="n">
         <v>6</v>
       </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>La parte que le toca al barrio del mantenimiento que hace el Fideicomiso (personal y gastos) en los espacios del barrio.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -24092,6 +24109,11 @@
       <c r="D8" t="n">
         <v>7</v>
       </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>La parte que le toca al barrio del mantenimiento de los espacios comunes de todo el predio.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -24112,6 +24134,11 @@
       <c r="D9" t="n">
         <v>8</v>
       </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Sistema que usa la administración para liquidar y publicar las expensas.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -24132,6 +24159,11 @@
       <c r="D10" t="n">
         <v>9</v>
       </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Internet para las cámaras de seguridad.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -24152,6 +24184,11 @@
       <c r="D11" t="n">
         <v>10</v>
       </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>La parte del barrio en gastos menores del Fideicomiso: combustible, ferretería, reparaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -24172,6 +24209,11 @@
       <c r="D12" t="n">
         <v>11</v>
       </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Reparación del control remoto del portón (materiales y mano de obra).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -24192,6 +24234,11 @@
       <c r="D13" t="n">
         <v>12</v>
       </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Reparación del portón de entrada de vehículos.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -24212,6 +24259,11 @@
       <c r="D14" t="n">
         <v>13</v>
       </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Lo que cobra la administración por su trabajo.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -24232,6 +24284,11 @@
       <c r="D15" t="n">
         <v>14</v>
       </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Mantenimiento de la cuenta, comisiones e impuestos del Banco Galicia.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -24252,6 +24309,11 @@
       <c r="D16" t="n">
         <v>15</v>
       </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Comisiones por cobrar las expensas (Pago Fácil, Rapipago, transferencias) e impuestos del Banco Roela.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -24272,6 +24334,11 @@
       <c r="D17" t="n">
         <v>16</v>
       </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Seguro que cubre al barrio si alguien sufre un daño dentro de él.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -24292,6 +24359,11 @@
       <c r="D18" t="n">
         <v>17</v>
       </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Agua para la garita de la guardia.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -24312,6 +24384,11 @@
       <c r="D19" t="n">
         <v>18</v>
       </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Trabajo de obra civil para la instalación de las cámaras de seguridad.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -24332,6 +24409,11 @@
       <c r="D20" t="n">
         <v>19</v>
       </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Compra de equipos para el puesto de monitoreo de las cámaras.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -24351,6 +24433,11 @@
       </c>
       <c r="D21" t="n">
         <v>20</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Servicio de vigilancia del barrio, a cargo de la empresa de seguridad.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -24482,16 +24569,16 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>ID_Carga</t>
+          <t>ID_Linea</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -24506,27 +24593,27 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Fecha</t>
+          <t>Concepto</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>Usuario</t>
+          <t>Explicacion</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>Archivo_ID</t>
+          <t>Ahorrable</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Ahorro_Estimado</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>Resumen</t>
+          <t>Nota_Ahorro</t>
         </is>
       </c>
     </row>
@@ -24783,6 +24870,126 @@
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID_Expensa</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Barrio</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Mensaje</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Fecha_Publicacion</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID_Carga</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Barrio</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Usuario</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Archivo_ID</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Resumen</t>
         </is>
       </c>
     </row>
